--- a/artfynd/A 57073-2023 artfynd.xlsx
+++ b/artfynd/A 57073-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 57073-2023 artfynd.xlsx
+++ b/artfynd/A 57073-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1345,6 +1345,117 @@
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>118983301</v>
+      </c>
+      <c r="B8" t="n">
+        <v>57290</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Fiskhusberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>551102</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7027477</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 57073-2023 artfynd.xlsx
+++ b/artfynd/A 57073-2023 artfynd.xlsx
@@ -1014,7 +1014,7 @@
         <v>103986830</v>
       </c>
       <c r="B5" t="n">
-        <v>80221</v>
+        <v>80222</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 57073-2023 artfynd.xlsx
+++ b/artfynd/A 57073-2023 artfynd.xlsx
@@ -1014,7 +1014,7 @@
         <v>103986830</v>
       </c>
       <c r="B5" t="n">
-        <v>80222</v>
+        <v>80224</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 57073-2023 artfynd.xlsx
+++ b/artfynd/A 57073-2023 artfynd.xlsx
@@ -1014,7 +1014,7 @@
         <v>103986830</v>
       </c>
       <c r="B5" t="n">
-        <v>80224</v>
+        <v>80225</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 57073-2023 artfynd.xlsx
+++ b/artfynd/A 57073-2023 artfynd.xlsx
@@ -1014,7 +1014,7 @@
         <v>103986830</v>
       </c>
       <c r="B5" t="n">
-        <v>80225</v>
+        <v>80226</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 57073-2023 artfynd.xlsx
+++ b/artfynd/A 57073-2023 artfynd.xlsx
@@ -1014,7 +1014,7 @@
         <v>103986830</v>
       </c>
       <c r="B5" t="n">
-        <v>80226</v>
+        <v>80229</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 57073-2023 artfynd.xlsx
+++ b/artfynd/A 57073-2023 artfynd.xlsx
@@ -1014,7 +1014,7 @@
         <v>103986830</v>
       </c>
       <c r="B5" t="n">
-        <v>80229</v>
+        <v>80230</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 57073-2023 artfynd.xlsx
+++ b/artfynd/A 57073-2023 artfynd.xlsx
@@ -1014,7 +1014,7 @@
         <v>103986830</v>
       </c>
       <c r="B5" t="n">
-        <v>80230</v>
+        <v>80236</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 57073-2023 artfynd.xlsx
+++ b/artfynd/A 57073-2023 artfynd.xlsx
@@ -1014,7 +1014,7 @@
         <v>103986830</v>
       </c>
       <c r="B5" t="n">
-        <v>80236</v>
+        <v>80237</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 57073-2023 artfynd.xlsx
+++ b/artfynd/A 57073-2023 artfynd.xlsx
@@ -1014,7 +1014,7 @@
         <v>103986830</v>
       </c>
       <c r="B5" t="n">
-        <v>80237</v>
+        <v>80240</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 57073-2023 artfynd.xlsx
+++ b/artfynd/A 57073-2023 artfynd.xlsx
@@ -1014,7 +1014,7 @@
         <v>103986830</v>
       </c>
       <c r="B5" t="n">
-        <v>80240</v>
+        <v>80242</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 57073-2023 artfynd.xlsx
+++ b/artfynd/A 57073-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,50 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>103986832</v>
+        <v>103986830</v>
       </c>
       <c r="B2" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80303</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>389</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Läderlappslav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Collema nigrescens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Huds.) DC.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Köttsjön, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>551138.6229313782</v>
+        <v>551093</v>
       </c>
       <c r="R2" t="n">
-        <v>7027510.095691863</v>
+        <v>7027429</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,27 +746,18 @@
           <t>2022-09-20</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2022-09-20</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
-        <v>0</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -787,15 +776,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>103986827</v>
+        <v>103986829</v>
       </c>
       <c r="B3" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -803,21 +787,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +811,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>550823.8484205611</v>
+        <v>550897</v>
       </c>
       <c r="R3" t="n">
-        <v>7027499.255275433</v>
+        <v>7027453</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -860,19 +844,9 @@
           <t>2022-09-20</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2022-09-20</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,15 +873,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>103986829</v>
+        <v>104044304</v>
       </c>
       <c r="B4" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -935,14 +904,14 @@
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Köttsjön, Jmt</t>
+          <t>Rävatjärnbrännan, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>550896.4706674087</v>
+        <v>551005</v>
       </c>
       <c r="R4" t="n">
-        <v>7027452.847932362</v>
+        <v>7027452</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -969,22 +938,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2022-09-20</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-10-04</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2022-09-20</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-10-04</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -999,60 +958,57 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Maria Edstam</t>
+          <t>Ulrika Westling</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Maria Edstam</t>
+          <t>Ulrika Westling</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>103986830</v>
+        <v>104044305</v>
       </c>
       <c r="B5" t="n">
-        <v>80242</v>
+        <v>91909</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>389</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Läderlappslav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Collema nigrescens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Huds.) DC.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Köttsjön, Jmt</t>
+          <t>Rävatjärnbrännan, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>551093</v>
+        <v>550836</v>
       </c>
       <c r="R5" t="n">
-        <v>7027429</v>
+        <v>7027503</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1079,48 +1035,42 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2022-09-20</t>
+          <t>2022-10-04</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2022-09-20</t>
+          <t>2022-10-04</t>
         </is>
       </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
-        <v>1</v>
-      </c>
-      <c r="AF5" t="inlineStr"/>
+        <v>0</v>
+      </c>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Maria Edstam</t>
+          <t>Ulrika Westling</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Maria Edstam</t>
+          <t>Ulrika Westling</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>104044305</v>
+        <v>103986832</v>
       </c>
       <c r="B6" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1128,34 +1078,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Rävatjärnbrännan, Jmt</t>
+          <t>Köttsjön, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>550835.9190686973</v>
+        <v>551139</v>
       </c>
       <c r="R6" t="n">
-        <v>7027503.036130862</v>
+        <v>7027510</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1182,22 +1132,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2022-10-04</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-09-20</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2022-10-04</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-09-20</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1212,27 +1152,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Ulrika Westling</t>
+          <t>Maria Edstam</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Ulrika Westling</t>
+          <t>Maria Edstam</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>104044304</v>
+        <v>118983301</v>
       </c>
       <c r="B7" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1240,34 +1175,38 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Rävatjärnbrännan, Jmt</t>
+          <t>Fiskhusberget, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>551005.6560970428</v>
+        <v>551102</v>
       </c>
       <c r="R7" t="n">
-        <v>7027452.340452629</v>
+        <v>7027477</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1294,22 +1233,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2022-10-04</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-08-07</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2022-10-04</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1324,126 +1258,15 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Ulrika Westling</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Ulrika Westling</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>118983301</v>
-      </c>
-      <c r="B8" t="n">
-        <v>57308</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E8" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>Fiskhusberget, Jmt</t>
-        </is>
-      </c>
-      <c r="Q8" t="n">
-        <v>551102</v>
-      </c>
-      <c r="R8" t="n">
-        <v>7027477</v>
-      </c>
-      <c r="S8" t="n">
-        <v>10</v>
-      </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>Ragunda</t>
-        </is>
-      </c>
-      <c r="V8" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>Ragunda</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>2024-08-07</t>
-        </is>
-      </c>
-      <c r="AA8" t="inlineStr">
-        <is>
-          <t>2024-08-07</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
-        </is>
-      </c>
-      <c r="AD8" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE8" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG8" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT8" t="inlineStr"/>
-      <c r="AW8" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX8" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 57073-2023 artfynd.xlsx
+++ b/artfynd/A 57073-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -773,6 +778,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103986830</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -870,6 +880,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103986829</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -967,6 +982,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104044304</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1064,6 +1084,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104044305</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1161,6 +1186,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103986832</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1267,8 +1297,21 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118983301</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>